--- a/LongWire_9to1_UnUn_Calculator.xlsx
+++ b/LongWire_9to1_UnUn_Calculator.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="1" state="visible" r:id="rId3"/>
@@ -1306,7 +1306,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1613,6 +1613,14 @@
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1983,11 +1991,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="47309874"/>
-        <c:axId val="43796044"/>
+        <c:axId val="93293734"/>
+        <c:axId val="83200353"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="47309874"/>
+        <c:axId val="93293734"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2052,7 +2060,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43796044"/>
+        <c:crossAx val="83200353"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2060,7 +2068,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43796044"/>
+        <c:axId val="83200353"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="12"/>
@@ -2136,7 +2144,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47309874"/>
+        <c:crossAx val="93293734"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1.5"/>
@@ -2201,9 +2209,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>376200</xdr:colOff>
+      <xdr:colOff>375840</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>126720</xdr:rowOff>
+      <xdr:rowOff>126360</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2211,8 +2219,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="5290200"/>
-        <a:ext cx="7777080" cy="4317840"/>
+        <a:off x="0" y="5292720"/>
+        <a:ext cx="7776720" cy="4317480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2494,7 +2502,7 @@
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
     </row>
-    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
         <v>8</v>
       </c>
@@ -2506,7 +2514,7 @@
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
     </row>
-    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
         <v>9</v>
       </c>
@@ -2532,7 +2540,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
         <v>17</v>
       </c>
@@ -2562,7 +2570,7 @@
         <v>40.625</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
         <v>19</v>
       </c>
@@ -2592,7 +2600,7 @@
         <v>20.8928571428571</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
         <v>20</v>
       </c>
@@ -2622,7 +2630,7 @@
         <v>13.664393160796</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
         <v>21</v>
       </c>
@@ -2652,7 +2660,7 @@
         <v>10.4464285714286</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
         <v>22</v>
       </c>
@@ -2682,7 +2690,7 @@
         <v>7.24009900990099</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
         <v>24</v>
       </c>
@@ -2712,7 +2720,7 @@
         <v>5.22321428571429</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
         <v>25</v>
       </c>
@@ -2742,7 +2750,7 @@
         <v>4.04721053796768</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
         <v>26</v>
       </c>
@@ -2772,7 +2780,7 @@
         <v>3.48214285714286</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
         <v>27</v>
       </c>
@@ -2802,7 +2810,7 @@
         <v>2.93792687826436</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
         <v>28</v>
       </c>
@@ -2832,7 +2840,7 @@
         <v>2.61160714285714</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
         <v>29</v>
       </c>
@@ -2862,7 +2870,7 @@
         <v>1.4625</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21"/>
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
@@ -2906,7 +2914,7 @@
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
     </row>
-    <row r="26" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
         <v>34</v>
       </c>
@@ -2935,7 +2943,7 @@
       <c r="G28" s="27"/>
       <c r="H28" s="27"/>
     </row>
-    <row r="29" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
         <v>37</v>
       </c>
@@ -2961,7 +2969,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="s">
         <v>45</v>
       </c>
@@ -2994,7 +3002,7 @@
         <v>Long wire – max performance</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="s">
         <v>46</v>
       </c>
@@ -3027,7 +3035,7 @@
         <v>Excellent home station</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="35" t="s">
         <v>47</v>
       </c>
@@ -3060,7 +3068,7 @@
         <v>Good portable/home</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="35" t="s">
         <v>48</v>
       </c>
@@ -3093,7 +3101,7 @@
         <v>Good portable/home</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="41" t="s">
         <v>49</v>
       </c>
@@ -3126,7 +3134,7 @@
         <v>Long wire – max performance</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="47" t="s">
         <v>50</v>
       </c>
@@ -3243,7 +3251,7 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="52" t="s">
         <v>9</v>
       </c>
@@ -10703,19 +10711,20 @@
   <dimension ref="A1:E49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="77" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="77" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="77" width="38"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="78" width="8.68"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="77" t="s">
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
@@ -10726,125 +10735,125 @@
       <c r="D2" s="27"/>
       <c r="E2" s="27"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="78" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="E3" s="79"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="80" t="s">
+      <c r="E3" s="81"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="80" t="s">
+      <c r="C4" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="80" t="s">
+      <c r="D4" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="80"/>
-    </row>
-    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="81" t="s">
+      <c r="E4" s="82"/>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="81" t="s">
+      <c r="C5" s="83" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="81"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="80" t="s">
+      <c r="E5" s="83"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="82" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="82" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="80" t="s">
+      <c r="C6" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="80" t="s">
+      <c r="D6" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="80"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="81" t="s">
+      <c r="E6" s="82"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="83" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="81" t="s">
+      <c r="B7" s="83" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="81" t="s">
+      <c r="C7" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="E7" s="81"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="80" t="s">
+      <c r="E7" s="83"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="80" t="s">
+      <c r="C8" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="80" t="s">
+      <c r="D8" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="80"/>
-    </row>
-    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="81" t="s">
+      <c r="E8" s="82"/>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="83" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="83" t="s">
         <v>113</v>
       </c>
-      <c r="C9" s="81" t="s">
+      <c r="C9" s="83" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="81" t="s">
+      <c r="D9" s="83" t="s">
         <v>115</v>
       </c>
-      <c r="E9" s="81"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="80" t="s">
+      <c r="E9" s="83"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="80" t="s">
+      <c r="B10" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="80" t="s">
+      <c r="C10" s="82" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="80" t="s">
+      <c r="D10" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="E10" s="80"/>
+      <c r="E10" s="82"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
@@ -10855,105 +10864,105 @@
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="78" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="B13" s="79" t="s">
+      <c r="B13" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="C13" s="79" t="s">
+      <c r="C13" s="81" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="79" t="s">
+      <c r="D13" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="E13" s="79" t="s">
+      <c r="E13" s="81" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="80" t="s">
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="B14" s="80" t="s">
+      <c r="B14" s="82" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="80" t="s">
+      <c r="C14" s="82" t="s">
         <v>128</v>
       </c>
-      <c r="D14" s="80" t="s">
+      <c r="D14" s="82" t="s">
         <v>129</v>
       </c>
-      <c r="E14" s="80" t="s">
+      <c r="E14" s="82" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="81" t="s">
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="83" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="83" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="81" t="s">
+      <c r="C15" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="D15" s="81" t="s">
+      <c r="D15" s="83" t="s">
         <v>134</v>
       </c>
-      <c r="E15" s="81" t="s">
+      <c r="E15" s="83" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="80" t="s">
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="B16" s="80" t="s">
+      <c r="B16" s="82" t="s">
         <v>137</v>
       </c>
-      <c r="C16" s="80" t="s">
+      <c r="C16" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="D16" s="80" t="s">
+      <c r="D16" s="82" t="s">
         <v>139</v>
       </c>
-      <c r="E16" s="80" t="s">
+      <c r="E16" s="82" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="81" t="s">
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="83" t="s">
         <v>141</v>
       </c>
-      <c r="B17" s="81" t="s">
+      <c r="B17" s="83" t="s">
         <v>142</v>
       </c>
-      <c r="C17" s="81" t="s">
+      <c r="C17" s="83" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="81" t="s">
+      <c r="D17" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="E17" s="81" t="s">
+      <c r="E17" s="83" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="80" t="s">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="82" t="s">
         <v>146</v>
       </c>
-      <c r="B18" s="80" t="s">
+      <c r="B18" s="82" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="80" t="s">
+      <c r="C18" s="82" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="80" t="s">
+      <c r="D18" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="E18" s="80" t="s">
+      <c r="E18" s="82" t="s">
         <v>150</v>
       </c>
     </row>
@@ -10966,207 +10975,207 @@
       <c r="D20" s="27"/>
       <c r="E20" s="27"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="78" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="79" t="s">
+      <c r="B21" s="81" t="s">
         <v>152</v>
       </c>
-      <c r="C21" s="79" t="s">
+      <c r="C21" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="D21" s="79" t="s">
+      <c r="D21" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="E21" s="79" t="s">
+      <c r="E21" s="81" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="80" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="80" t="s">
+      <c r="B22" s="82" t="s">
         <v>155</v>
       </c>
-      <c r="C22" s="80" t="s">
+      <c r="C22" s="82" t="s">
         <v>156</v>
       </c>
-      <c r="D22" s="80" t="s">
+      <c r="D22" s="82" t="s">
         <v>157</v>
       </c>
-      <c r="E22" s="80" t="s">
+      <c r="E22" s="82" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="81" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="81" t="s">
+      <c r="B23" s="83" t="s">
         <v>159</v>
       </c>
-      <c r="C23" s="81" t="s">
+      <c r="C23" s="83" t="s">
         <v>160</v>
       </c>
-      <c r="D23" s="81" t="s">
+      <c r="D23" s="83" t="s">
         <v>161</v>
       </c>
-      <c r="E23" s="81" t="s">
+      <c r="E23" s="83" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="80" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="80" t="s">
+      <c r="B24" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="80" t="s">
+      <c r="C24" s="82" t="s">
         <v>164</v>
       </c>
-      <c r="D24" s="80" t="s">
+      <c r="D24" s="82" t="s">
         <v>165</v>
       </c>
-      <c r="E24" s="80" t="s">
+      <c r="E24" s="82" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="81" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="81" t="s">
+      <c r="B25" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="C25" s="81" t="s">
+      <c r="C25" s="83" t="s">
         <v>168</v>
       </c>
-      <c r="D25" s="81" t="s">
+      <c r="D25" s="83" t="s">
         <v>169</v>
       </c>
-      <c r="E25" s="81" t="s">
+      <c r="E25" s="83" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="80" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="80" t="s">
+      <c r="B26" s="82" t="s">
         <v>171</v>
       </c>
-      <c r="C26" s="80" t="s">
+      <c r="C26" s="82" t="s">
         <v>172</v>
       </c>
-      <c r="D26" s="80" t="s">
+      <c r="D26" s="82" t="s">
         <v>173</v>
       </c>
-      <c r="E26" s="80" t="s">
+      <c r="E26" s="82" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="81" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="81" t="s">
+      <c r="B27" s="83" t="s">
         <v>175</v>
       </c>
-      <c r="C27" s="81" t="s">
+      <c r="C27" s="83" t="s">
         <v>176</v>
       </c>
-      <c r="D27" s="81" t="s">
+      <c r="D27" s="83" t="s">
         <v>177</v>
       </c>
-      <c r="E27" s="81" t="s">
+      <c r="E27" s="83" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="80" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="80" t="s">
+      <c r="B28" s="82" t="s">
         <v>179</v>
       </c>
-      <c r="C28" s="80" t="s">
+      <c r="C28" s="82" t="s">
         <v>180</v>
       </c>
-      <c r="D28" s="80" t="s">
+      <c r="D28" s="82" t="s">
         <v>181</v>
       </c>
-      <c r="E28" s="80" t="s">
+      <c r="E28" s="82" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="81" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="81" t="s">
+      <c r="B29" s="83" t="s">
         <v>183</v>
       </c>
-      <c r="C29" s="81" t="s">
+      <c r="C29" s="83" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="81" t="s">
+      <c r="D29" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="E29" s="81" t="s">
+      <c r="E29" s="83" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="80" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="80" t="s">
+      <c r="B30" s="82" t="s">
         <v>187</v>
       </c>
-      <c r="C30" s="80" t="s">
+      <c r="C30" s="82" t="s">
         <v>188</v>
       </c>
-      <c r="D30" s="80" t="s">
+      <c r="D30" s="82" t="s">
         <v>189</v>
       </c>
-      <c r="E30" s="80" t="s">
+      <c r="E30" s="82" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="81" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="81" t="s">
+      <c r="B31" s="83" t="s">
         <v>191</v>
       </c>
-      <c r="C31" s="81" t="s">
+      <c r="C31" s="83" t="s">
         <v>192</v>
       </c>
-      <c r="D31" s="81" t="s">
+      <c r="D31" s="83" t="s">
         <v>193</v>
       </c>
-      <c r="E31" s="81" t="s">
+      <c r="E31" s="83" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="80" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="80" t="s">
+      <c r="B32" s="82" t="s">
         <v>195</v>
       </c>
-      <c r="C32" s="80" t="s">
+      <c r="C32" s="82" t="s">
         <v>196</v>
       </c>
-      <c r="D32" s="80" t="s">
+      <c r="D32" s="82" t="s">
         <v>197</v>
       </c>
-      <c r="E32" s="80" t="s">
+      <c r="E32" s="82" t="s">
         <v>198</v>
       </c>
     </row>
@@ -11179,88 +11188,88 @@
       <c r="D34" s="25"/>
       <c r="E34" s="25"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="78" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="80" t="s">
         <v>200</v>
       </c>
-      <c r="B35" s="79" t="s">
+      <c r="B35" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="C35" s="79" t="s">
+      <c r="C35" s="81" t="s">
         <v>202</v>
       </c>
-      <c r="D35" s="79" t="s">
+      <c r="D35" s="81" t="s">
         <v>203</v>
       </c>
-      <c r="E35" s="79" t="s">
+      <c r="E35" s="81" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="80" t="s">
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="82" t="s">
         <v>205</v>
       </c>
-      <c r="B36" s="80" t="s">
+      <c r="B36" s="82" t="s">
         <v>206</v>
       </c>
-      <c r="C36" s="80" t="s">
+      <c r="C36" s="82" t="s">
         <v>207</v>
       </c>
-      <c r="D36" s="80" t="s">
+      <c r="D36" s="82" t="s">
         <v>208</v>
       </c>
-      <c r="E36" s="80" t="s">
+      <c r="E36" s="82" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="81" t="s">
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="83" t="s">
         <v>210</v>
       </c>
-      <c r="B37" s="81" t="s">
+      <c r="B37" s="83" t="s">
         <v>211</v>
       </c>
-      <c r="C37" s="81" t="s">
+      <c r="C37" s="83" t="s">
         <v>212</v>
       </c>
-      <c r="D37" s="81" t="s">
+      <c r="D37" s="83" t="s">
         <v>213</v>
       </c>
-      <c r="E37" s="81" t="s">
+      <c r="E37" s="83" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="80" t="s">
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="82" t="s">
         <v>215</v>
       </c>
-      <c r="B38" s="80" t="s">
+      <c r="B38" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="C38" s="80" t="s">
+      <c r="C38" s="82" t="s">
         <v>217</v>
       </c>
-      <c r="D38" s="80" t="s">
+      <c r="D38" s="82" t="s">
         <v>218</v>
       </c>
-      <c r="E38" s="80" t="s">
+      <c r="E38" s="82" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="81" t="s">
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="83" t="s">
         <v>220</v>
       </c>
-      <c r="B39" s="81" t="s">
+      <c r="B39" s="83" t="s">
         <v>221</v>
       </c>
-      <c r="C39" s="81" t="s">
+      <c r="C39" s="83" t="s">
         <v>222</v>
       </c>
-      <c r="D39" s="81" t="s">
+      <c r="D39" s="83" t="s">
         <v>223</v>
       </c>
-      <c r="E39" s="81" t="s">
+      <c r="E39" s="83" t="s">
         <v>224</v>
       </c>
     </row>
@@ -11273,124 +11282,124 @@
       <c r="D41" s="27"/>
       <c r="E41" s="27"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="78" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="80" t="s">
         <v>226</v>
       </c>
-      <c r="B42" s="79" t="s">
+      <c r="B42" s="81" t="s">
         <v>125</v>
       </c>
-      <c r="C42" s="79" t="s">
+      <c r="C42" s="81" t="s">
         <v>227</v>
       </c>
-      <c r="D42" s="79" t="s">
+      <c r="D42" s="81" t="s">
         <v>228</v>
       </c>
-      <c r="E42" s="79"/>
-    </row>
-    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="81" t="s">
+      <c r="E42" s="81"/>
+    </row>
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="83" t="s">
         <v>229</v>
       </c>
-      <c r="B43" s="81" t="s">
+      <c r="B43" s="83" t="s">
         <v>230</v>
       </c>
-      <c r="C43" s="81" t="s">
+      <c r="C43" s="83" t="s">
         <v>231</v>
       </c>
-      <c r="D43" s="81" t="s">
+      <c r="D43" s="83" t="s">
         <v>232</v>
       </c>
-      <c r="E43" s="81"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="80" t="s">
+      <c r="E43" s="83"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="82" t="s">
         <v>233</v>
       </c>
-      <c r="B44" s="80" t="s">
+      <c r="B44" s="82" t="s">
         <v>234</v>
       </c>
-      <c r="C44" s="80" t="s">
+      <c r="C44" s="82" t="s">
         <v>235</v>
       </c>
-      <c r="D44" s="80" t="s">
+      <c r="D44" s="82" t="s">
         <v>236</v>
       </c>
-      <c r="E44" s="80"/>
-    </row>
-    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="81" t="s">
+      <c r="E44" s="82"/>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="83" t="s">
         <v>237</v>
       </c>
-      <c r="B45" s="81" t="s">
+      <c r="B45" s="83" t="s">
         <v>238</v>
       </c>
-      <c r="C45" s="81" t="s">
+      <c r="C45" s="83" t="s">
         <v>239</v>
       </c>
-      <c r="D45" s="81" t="s">
+      <c r="D45" s="83" t="s">
         <v>240</v>
       </c>
-      <c r="E45" s="81"/>
-    </row>
-    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="80" t="s">
+      <c r="E45" s="83"/>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="82" t="s">
         <v>241</v>
       </c>
-      <c r="B46" s="80" t="s">
+      <c r="B46" s="82" t="s">
         <v>242</v>
       </c>
-      <c r="C46" s="80" t="s">
+      <c r="C46" s="82" t="s">
         <v>239</v>
       </c>
-      <c r="D46" s="80" t="s">
+      <c r="D46" s="82" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="80"/>
-    </row>
-    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="E46" s="82"/>
+    </row>
+    <row r="47" customFormat="false" ht="33.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="77" t="s">
         <v>244</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="77" t="s">
         <v>245</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="77" t="s">
         <v>246</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="77" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="81" t="s">
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="83" t="s">
         <v>248</v>
       </c>
-      <c r="B48" s="81" t="s">
+      <c r="B48" s="83" t="s">
         <v>249</v>
       </c>
-      <c r="C48" s="81" t="s">
+      <c r="C48" s="83" t="s">
         <v>246</v>
       </c>
-      <c r="D48" s="81" t="s">
+      <c r="D48" s="83" t="s">
         <v>250</v>
       </c>
-      <c r="E48" s="81"/>
-    </row>
-    <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="80" t="s">
+      <c r="E48" s="83"/>
+    </row>
+    <row r="49" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="82" t="s">
         <v>251</v>
       </c>
-      <c r="B49" s="80" t="s">
+      <c r="B49" s="82" t="s">
         <v>252</v>
       </c>
-      <c r="C49" s="80" t="s">
+      <c r="C49" s="82" t="s">
         <v>253</v>
       </c>
-      <c r="D49" s="80" t="s">
+      <c r="D49" s="82" t="s">
         <v>254</v>
       </c>
-      <c r="E49" s="80"/>
+      <c r="E49" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="6">
